--- a/диаграммы/диаграмма_ганта.xlsx
+++ b/диаграммы/диаграмма_ганта.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\Sveta\шарага\бдшки\неваляшка\bd_kursovaya\диаграммы\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF5CF24-A54E-4BCE-8E4D-F70EDF50316E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A34C2EA-1B6C-47BB-80FA-62B7582BD06C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{3A01D02B-9FAD-4C5E-934F-F571FF266AB6}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" activeTab="1" xr2:uid="{3A01D02B-9FAD-4C5E-934F-F571FF266AB6}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -64,10 +64,6 @@
     <t>Проектирование форм</t>
   </si>
   <si>
-    <t>Реализация БД и реализация
-запросов БД</t>
-  </si>
-  <si>
     <t>Оформление курсовой работы</t>
   </si>
   <si>
@@ -78,6 +74,9 @@
   </si>
   <si>
     <t>Концептуальное проектирование</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Реализация БД </t>
   </si>
 </sst>
 </file>
@@ -236,8 +235,7 @@
                   <c:v>Проектирование форм</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Реализация БД и реализация
-запросов БД</c:v>
+                  <c:v>Реализация БД </c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>Оформление курсовой работы</c:v>
@@ -338,8 +336,7 @@
                   <c:v>Проектирование форм</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Реализация БД и реализация
-запросов БД</c:v>
+                  <c:v>Реализация БД </c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>Оформление курсовой работы</c:v>
@@ -643,8 +640,7 @@
                   <c:v>Проектирование форм</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Реализация БД и реализация
-запросов БД</c:v>
+                  <c:v>Реализация БД </c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>Оформление курсовой работы</c:v>
@@ -745,8 +741,7 @@
                   <c:v>Проектирование форм</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Реализация БД и реализация
-запросов БД</c:v>
+                  <c:v>Реализация БД </c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>Оформление курсовой работы</c:v>
@@ -2464,7 +2459,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -2472,7 +2467,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4">
         <v>46034</v>
@@ -2508,7 +2503,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="4">
         <v>46048</v>
@@ -2593,12 +2588,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C9" s="4">
         <v>46099</v>
@@ -2616,7 +2611,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="4">
         <v>46120</v>
